--- a/data/final_data.xlsx
+++ b/data/final_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wilderhartwell/Documents/jellema2024/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{96BAE70D-8E95-774B-B66C-A9A0F780A01D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C32E0192-CF6D-3942-BEF6-839D8C59A411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1100" yWindow="900" windowWidth="28040" windowHeight="17180" xr2:uid="{7B2A0532-AFC8-E14C-966E-E35CF75FB092}"/>
+    <workbookView xWindow="15060" yWindow="820" windowWidth="15180" windowHeight="17840" xr2:uid="{7B2A0532-AFC8-E14C-966E-E35CF75FB092}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,6 +33,206 @@
     </ext>
   </extLst>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="65">
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Q_gender</t>
+  </si>
+  <si>
+    <t>Q_age</t>
+  </si>
+  <si>
+    <t>Q1</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Q3</t>
+  </si>
+  <si>
+    <t>Q4</t>
+  </si>
+  <si>
+    <t>Q5</t>
+  </si>
+  <si>
+    <t>Q6</t>
+  </si>
+  <si>
+    <t>Q7</t>
+  </si>
+  <si>
+    <t>Q8</t>
+  </si>
+  <si>
+    <t>Q9</t>
+  </si>
+  <si>
+    <t>Q10</t>
+  </si>
+  <si>
+    <t>attention_1</t>
+  </si>
+  <si>
+    <t>attention_2</t>
+  </si>
+  <si>
+    <t>attention_3</t>
+  </si>
+  <si>
+    <t>attention_4</t>
+  </si>
+  <si>
+    <t>rt_attention_1</t>
+  </si>
+  <si>
+    <t>rt_attention_2</t>
+  </si>
+  <si>
+    <t>rt_attention_3</t>
+  </si>
+  <si>
+    <t>rt_attention_4</t>
+  </si>
+  <si>
+    <t>frown50_1</t>
+  </si>
+  <si>
+    <t>smile50_1</t>
+  </si>
+  <si>
+    <t>frown50_2</t>
+  </si>
+  <si>
+    <t>smile50_2</t>
+  </si>
+  <si>
+    <t>rt_frown_1</t>
+  </si>
+  <si>
+    <t>rt_smile_1</t>
+  </si>
+  <si>
+    <t>rt_frown_2</t>
+  </si>
+  <si>
+    <t>rt_smile_2</t>
+  </si>
+  <si>
+    <t>frown50_1_cor</t>
+  </si>
+  <si>
+    <t>smile50_1_cor</t>
+  </si>
+  <si>
+    <t>frown50_2_cor</t>
+  </si>
+  <si>
+    <t>smile50_2_cor</t>
+  </si>
+  <si>
+    <t>CheckQ1</t>
+  </si>
+  <si>
+    <t>CheckQ2</t>
+  </si>
+  <si>
+    <t>3zmwaqv271</t>
+  </si>
+  <si>
+    <t>Man</t>
+  </si>
+  <si>
+    <t>35-44</t>
+  </si>
+  <si>
+    <t>Definitely Agree</t>
+  </si>
+  <si>
+    <t>Definitely Disagree</t>
+  </si>
+  <si>
+    <t>Slightly Disagree</t>
+  </si>
+  <si>
+    <t>Slightly Agree</t>
+  </si>
+  <si>
+    <t>Slightly Disagre</t>
+  </si>
+  <si>
+    <t>j</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>Negative</t>
+  </si>
+  <si>
+    <t>5gfekse2ql</t>
+  </si>
+  <si>
+    <t>Woman</t>
+  </si>
+  <si>
+    <t>45-54</t>
+  </si>
+  <si>
+    <t>Neutral</t>
+  </si>
+  <si>
+    <t>6ld5s60j5a</t>
+  </si>
+  <si>
+    <t>9dh7ecg3xr</t>
+  </si>
+  <si>
+    <t>9tpropomro</t>
+  </si>
+  <si>
+    <t>I do not know</t>
+  </si>
+  <si>
+    <t>18fwdebdv3</t>
+  </si>
+  <si>
+    <t>68ybbleft1</t>
+  </si>
+  <si>
+    <t>25-34</t>
+  </si>
+  <si>
+    <t>b5183qbwfj</t>
+  </si>
+  <si>
+    <t>dm31sblpep</t>
+  </si>
+  <si>
+    <t>dwfmm3lymt</t>
+  </si>
+  <si>
+    <t>eemkkolgs1</t>
+  </si>
+  <si>
+    <t>18-24</t>
+  </si>
+  <si>
+    <t>eomz4g57ck</t>
+  </si>
+  <si>
+    <t>"Question1":"Slightly Disagree","Question2":"Definitely Disagree","Question3":"Slightly Agree","Question4":"Slightly Agree","Question5":"Slightly Disagree","Question6":"Slightly Agree","Question7":"Definitely Agree","Question8":"Slightly Agree","Question9":"Definitely Agree","Question10":"Definitely Disagree"</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +602,1418 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03A0F602-C358-644E-9EF9-3D6D45D07AA0}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:M35"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F1" t="s">
+        <v>53</v>
+      </c>
+      <c r="G1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H1" t="s">
+        <v>56</v>
+      </c>
+      <c r="I1" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" t="s">
+        <v>59</v>
+      </c>
+      <c r="K1" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" t="s">
+        <v>61</v>
+      </c>
+      <c r="M1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F2" t="s">
+        <v>36</v>
+      </c>
+      <c r="G2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H2" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" t="s">
+        <v>48</v>
+      </c>
+      <c r="J2" t="s">
+        <v>36</v>
+      </c>
+      <c r="K2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>49</v>
+      </c>
+      <c r="F3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G3" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" t="s">
+        <v>57</v>
+      </c>
+      <c r="I3" t="s">
+        <v>57</v>
+      </c>
+      <c r="J3" t="s">
+        <v>37</v>
+      </c>
+      <c r="K3" t="s">
+        <v>49</v>
+      </c>
+      <c r="L3" t="s">
+        <v>62</v>
+      </c>
+      <c r="M3" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" t="s">
+        <v>40</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" t="s">
+        <v>40</v>
+      </c>
+      <c r="I4" t="s">
+        <v>39</v>
+      </c>
+      <c r="J4" t="s">
+        <v>40</v>
+      </c>
+      <c r="K4" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" t="s">
+        <v>41</v>
+      </c>
+      <c r="G5" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" t="s">
+        <v>40</v>
+      </c>
+      <c r="I5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K5" t="s">
+        <v>39</v>
+      </c>
+      <c r="L5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G6" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" t="s">
+        <v>41</v>
+      </c>
+      <c r="I6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J6" t="s">
+        <v>41</v>
+      </c>
+      <c r="K6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L6" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D7" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" t="s">
+        <v>41</v>
+      </c>
+      <c r="F7" t="s">
+        <v>38</v>
+      </c>
+      <c r="G7" t="s">
+        <v>41</v>
+      </c>
+      <c r="H7" t="s">
+        <v>41</v>
+      </c>
+      <c r="I7" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" t="s">
+        <v>40</v>
+      </c>
+      <c r="K7" t="s">
+        <v>41</v>
+      </c>
+      <c r="L7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>38</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" t="s">
+        <v>41</v>
+      </c>
+      <c r="G8" t="s">
+        <v>41</v>
+      </c>
+      <c r="H8" t="s">
+        <v>41</v>
+      </c>
+      <c r="I8" t="s">
+        <v>39</v>
+      </c>
+      <c r="J8" t="s">
+        <v>41</v>
+      </c>
+      <c r="K8" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>41</v>
+      </c>
+      <c r="C9" t="s">
+        <v>41</v>
+      </c>
+      <c r="D9" t="s">
+        <v>41</v>
+      </c>
+      <c r="E9" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" t="s">
+        <v>40</v>
+      </c>
+      <c r="G9" t="s">
+        <v>41</v>
+      </c>
+      <c r="H9" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9" t="s">
+        <v>38</v>
+      </c>
+      <c r="J9" t="s">
+        <v>40</v>
+      </c>
+      <c r="K9" t="s">
+        <v>40</v>
+      </c>
+      <c r="L9" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>41</v>
+      </c>
+      <c r="F10" t="s">
+        <v>40</v>
+      </c>
+      <c r="G10" t="s">
+        <v>41</v>
+      </c>
+      <c r="H10" t="s">
+        <v>41</v>
+      </c>
+      <c r="I10" t="s">
+        <v>41</v>
+      </c>
+      <c r="J10" t="s">
+        <v>41</v>
+      </c>
+      <c r="K10" t="s">
+        <v>41</v>
+      </c>
+      <c r="L10" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" t="s">
+        <v>41</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" t="s">
+        <v>40</v>
+      </c>
+      <c r="J11" t="s">
+        <v>41</v>
+      </c>
+      <c r="K11" t="s">
+        <v>40</v>
+      </c>
+      <c r="L11" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" t="s">
+        <v>40</v>
+      </c>
+      <c r="G12" t="s">
+        <v>41</v>
+      </c>
+      <c r="H12" t="s">
+        <v>41</v>
+      </c>
+      <c r="I12" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" t="s">
+        <v>41</v>
+      </c>
+      <c r="K12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" t="s">
+        <v>41</v>
+      </c>
+      <c r="F13" t="s">
+        <v>41</v>
+      </c>
+      <c r="G13" t="s">
+        <v>40</v>
+      </c>
+      <c r="H13" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" t="s">
+        <v>40</v>
+      </c>
+      <c r="J13" t="s">
+        <v>39</v>
+      </c>
+      <c r="K13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>1</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>1</v>
+      </c>
+      <c r="L14">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>1</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>1</v>
+      </c>
+      <c r="L15">
+        <v>1</v>
+      </c>
+      <c r="M15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16">
+        <v>1</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+      <c r="I16">
+        <v>1</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="K16">
+        <v>1</v>
+      </c>
+      <c r="L16">
+        <v>1</v>
+      </c>
+      <c r="M16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17">
+        <v>1</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>1</v>
+      </c>
+      <c r="I17">
+        <v>1</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
+      </c>
+      <c r="L17">
+        <v>1</v>
+      </c>
+      <c r="M17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>2010</v>
+      </c>
+      <c r="C18">
+        <v>3003</v>
+      </c>
+      <c r="D18">
+        <v>4409</v>
+      </c>
+      <c r="E18">
+        <v>3826</v>
+      </c>
+      <c r="F18">
+        <v>2811</v>
+      </c>
+      <c r="G18">
+        <v>2439</v>
+      </c>
+      <c r="H18">
+        <v>2866</v>
+      </c>
+      <c r="I18">
+        <v>3163</v>
+      </c>
+      <c r="J18">
+        <v>9600</v>
+      </c>
+      <c r="K18">
+        <v>4621</v>
+      </c>
+      <c r="L18">
+        <v>2487</v>
+      </c>
+      <c r="M18">
+        <v>2755</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>2226</v>
+      </c>
+      <c r="C19">
+        <v>3029</v>
+      </c>
+      <c r="D19">
+        <v>5136</v>
+      </c>
+      <c r="E19">
+        <v>2927</v>
+      </c>
+      <c r="F19">
+        <v>2986</v>
+      </c>
+      <c r="G19">
+        <v>1939</v>
+      </c>
+      <c r="H19">
+        <v>2529</v>
+      </c>
+      <c r="I19">
+        <v>3439</v>
+      </c>
+      <c r="J19">
+        <v>3848</v>
+      </c>
+      <c r="K19">
+        <v>6237</v>
+      </c>
+      <c r="L19">
+        <v>2538</v>
+      </c>
+      <c r="M19">
+        <v>5236</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>2461</v>
+      </c>
+      <c r="C20">
+        <v>2846</v>
+      </c>
+      <c r="D20">
+        <v>4906</v>
+      </c>
+      <c r="E20">
+        <v>2528</v>
+      </c>
+      <c r="F20">
+        <v>3449</v>
+      </c>
+      <c r="G20">
+        <v>3032</v>
+      </c>
+      <c r="H20">
+        <v>3184</v>
+      </c>
+      <c r="I20">
+        <v>4285</v>
+      </c>
+      <c r="J20">
+        <v>4357</v>
+      </c>
+      <c r="K20">
+        <v>3250</v>
+      </c>
+      <c r="L20">
+        <v>2491</v>
+      </c>
+      <c r="M20">
+        <v>3220</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>1890</v>
+      </c>
+      <c r="C21">
+        <v>2662</v>
+      </c>
+      <c r="D21">
+        <v>7393</v>
+      </c>
+      <c r="E21">
+        <v>2347</v>
+      </c>
+      <c r="F21">
+        <v>3693</v>
+      </c>
+      <c r="G21">
+        <v>2473</v>
+      </c>
+      <c r="H21">
+        <v>2615</v>
+      </c>
+      <c r="I21">
+        <v>3427</v>
+      </c>
+      <c r="J21">
+        <v>31302</v>
+      </c>
+      <c r="K21">
+        <v>2462</v>
+      </c>
+      <c r="L21">
+        <v>3958</v>
+      </c>
+      <c r="M21">
+        <v>3486</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="s">
+        <v>44</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" t="s">
+        <v>44</v>
+      </c>
+      <c r="F22" t="s">
+        <v>44</v>
+      </c>
+      <c r="G22" t="s">
+        <v>44</v>
+      </c>
+      <c r="H22" t="s">
+        <v>44</v>
+      </c>
+      <c r="I22" t="s">
+        <v>44</v>
+      </c>
+      <c r="J22" t="s">
+        <v>43</v>
+      </c>
+      <c r="K22" t="s">
+        <v>44</v>
+      </c>
+      <c r="L22" t="s">
+        <v>43</v>
+      </c>
+      <c r="M22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="s">
+        <v>43</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>44</v>
+      </c>
+      <c r="F23" t="s">
+        <v>43</v>
+      </c>
+      <c r="G23" t="s">
+        <v>43</v>
+      </c>
+      <c r="H23" t="s">
+        <v>44</v>
+      </c>
+      <c r="I23" t="s">
+        <v>44</v>
+      </c>
+      <c r="J23" t="s">
+        <v>43</v>
+      </c>
+      <c r="K23" t="s">
+        <v>44</v>
+      </c>
+      <c r="L23" t="s">
+        <v>43</v>
+      </c>
+      <c r="M23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="s">
+        <v>44</v>
+      </c>
+      <c r="D24" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G24" t="s">
+        <v>44</v>
+      </c>
+      <c r="H24" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" t="s">
+        <v>44</v>
+      </c>
+      <c r="J24" t="s">
+        <v>44</v>
+      </c>
+      <c r="K24" t="s">
+        <v>44</v>
+      </c>
+      <c r="L24" t="s">
+        <v>43</v>
+      </c>
+      <c r="M24" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B25" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E25" t="s">
+        <v>44</v>
+      </c>
+      <c r="F25" t="s">
+        <v>43</v>
+      </c>
+      <c r="G25" t="s">
+        <v>43</v>
+      </c>
+      <c r="H25" t="s">
+        <v>44</v>
+      </c>
+      <c r="I25" t="s">
+        <v>43</v>
+      </c>
+      <c r="J25" t="s">
+        <v>44</v>
+      </c>
+      <c r="K25" t="s">
+        <v>43</v>
+      </c>
+      <c r="L25" t="s">
+        <v>44</v>
+      </c>
+      <c r="M25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" t="s">
+        <v>25</v>
+      </c>
+      <c r="B26">
+        <v>3722</v>
+      </c>
+      <c r="C26">
+        <v>2400</v>
+      </c>
+      <c r="D26">
+        <v>535</v>
+      </c>
+      <c r="E26">
+        <v>2685</v>
+      </c>
+      <c r="F26">
+        <v>7143</v>
+      </c>
+      <c r="G26">
+        <v>5052</v>
+      </c>
+      <c r="H26">
+        <v>2825</v>
+      </c>
+      <c r="I26">
+        <v>103</v>
+      </c>
+      <c r="J26">
+        <v>3354</v>
+      </c>
+      <c r="K26">
+        <v>9525</v>
+      </c>
+      <c r="L26">
+        <v>2243</v>
+      </c>
+      <c r="M26">
+        <v>760</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27">
+        <v>4346</v>
+      </c>
+      <c r="C27">
+        <v>3279</v>
+      </c>
+      <c r="D27">
+        <v>537</v>
+      </c>
+      <c r="E27">
+        <v>2277</v>
+      </c>
+      <c r="F27">
+        <v>7682</v>
+      </c>
+      <c r="G27">
+        <v>647</v>
+      </c>
+      <c r="H27">
+        <v>5000</v>
+      </c>
+      <c r="I27">
+        <v>2923</v>
+      </c>
+      <c r="J27">
+        <v>563</v>
+      </c>
+      <c r="K27">
+        <v>796</v>
+      </c>
+      <c r="L27">
+        <v>2327</v>
+      </c>
+      <c r="M27">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>27</v>
+      </c>
+      <c r="B28">
+        <v>2726</v>
+      </c>
+      <c r="C28">
+        <v>2221</v>
+      </c>
+      <c r="D28">
+        <v>508</v>
+      </c>
+      <c r="E28">
+        <v>667</v>
+      </c>
+      <c r="F28">
+        <v>3836</v>
+      </c>
+      <c r="G28">
+        <v>747</v>
+      </c>
+      <c r="H28">
+        <v>5692</v>
+      </c>
+      <c r="I28">
+        <v>3880</v>
+      </c>
+      <c r="J28">
+        <v>5325</v>
+      </c>
+      <c r="K28">
+        <v>1657</v>
+      </c>
+      <c r="L28">
+        <v>3164</v>
+      </c>
+      <c r="M28">
+        <v>7750</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>28</v>
+      </c>
+      <c r="B29">
+        <v>4293</v>
+      </c>
+      <c r="C29">
+        <v>2720</v>
+      </c>
+      <c r="D29">
+        <v>570</v>
+      </c>
+      <c r="E29">
+        <v>1056</v>
+      </c>
+      <c r="F29">
+        <v>3019</v>
+      </c>
+      <c r="G29">
+        <v>693</v>
+      </c>
+      <c r="H29">
+        <v>7728</v>
+      </c>
+      <c r="I29">
+        <v>5938</v>
+      </c>
+      <c r="J29">
+        <v>10842</v>
+      </c>
+      <c r="K29">
+        <v>5482</v>
+      </c>
+      <c r="L29">
+        <v>1800</v>
+      </c>
+      <c r="M29">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>29</v>
+      </c>
+      <c r="B30" t="b">
+        <v>1</v>
+      </c>
+      <c r="C30" t="b">
+        <v>0</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="b">
+        <v>1</v>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+      <c r="L30" t="b">
+        <v>1</v>
+      </c>
+      <c r="M30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>30</v>
+      </c>
+      <c r="B31" t="b">
+        <v>0</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
+      </c>
+      <c r="F31" t="b">
+        <v>0</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="b">
+        <v>1</v>
+      </c>
+      <c r="J31" t="b">
+        <v>0</v>
+      </c>
+      <c r="K31" t="b">
+        <v>1</v>
+      </c>
+      <c r="L31" t="b">
+        <v>0</v>
+      </c>
+      <c r="M31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>31</v>
+      </c>
+      <c r="B32" t="b">
+        <v>1</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+      <c r="E32" t="b">
+        <v>0</v>
+      </c>
+      <c r="F32" t="b">
+        <v>0</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="b">
+        <v>0</v>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+      <c r="L32" t="b">
+        <v>0</v>
+      </c>
+      <c r="M32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>32</v>
+      </c>
+      <c r="B33" t="b">
+        <v>1</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="b">
+        <v>1</v>
+      </c>
+      <c r="K33" t="b">
+        <v>0</v>
+      </c>
+      <c r="L33" t="b">
+        <v>1</v>
+      </c>
+      <c r="M33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34" t="s">
+        <v>50</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" t="s">
+        <v>46</v>
+      </c>
+      <c r="G34" t="s">
+        <v>46</v>
+      </c>
+      <c r="H34" t="s">
+        <v>50</v>
+      </c>
+      <c r="I34" t="s">
+        <v>50</v>
+      </c>
+      <c r="J34" t="s">
+        <v>46</v>
+      </c>
+      <c r="K34" t="s">
+        <v>50</v>
+      </c>
+      <c r="L34" t="s">
+        <v>50</v>
+      </c>
+      <c r="M34" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C35" t="s">
+        <v>50</v>
+      </c>
+      <c r="D35" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" t="s">
+        <v>54</v>
+      </c>
+      <c r="G35" t="s">
+        <v>45</v>
+      </c>
+      <c r="H35" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" t="s">
+        <v>45</v>
+      </c>
+      <c r="J35" t="s">
+        <v>46</v>
+      </c>
+      <c r="K35" t="s">
+        <v>45</v>
+      </c>
+      <c r="L35" t="s">
+        <v>50</v>
+      </c>
+      <c r="M35" t="s">
+        <v>45</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>